--- a/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/GT/XD_PWM_TEST_250320.xlsx
+++ b/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/GT/XD_PWM_TEST_250320.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev\Docs\GT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_PWM_Rev_0\Docs\GT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09BB1CE9-DC65-4026-8DBB-2EC28ED21824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DBCD40-5D6A-41D7-8BC0-70116F186E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Plan" sheetId="2" r:id="rId1"/>

--- a/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/GT/XD_PWM_TEST_250320.xlsx
+++ b/XD_JIG/XD04/XD04_PWM_Rev_0/Docs/GT/XD_PWM_TEST_250320.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_PWM_Rev_0\Docs\GT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DBCD40-5D6A-41D7-8BC0-70116F186E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF93FF9D-1D04-4CB6-A823-9AD26B60A1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1416,6 +1416,33 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1442,33 +1469,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2090,35 +2090,35 @@
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="36"/>
     </row>
     <row r="3" spans="2:10" ht="17.25" thickBot="1">
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="19.05" customHeight="1" thickBot="1">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="45"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="33"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="46" t="s">
+      <c r="H4" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="I4" s="47"/>
-      <c r="J4" s="48"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="39"/>
     </row>
     <row r="5" spans="2:10">
       <c r="B5" s="3" t="s">
@@ -2184,13 +2184,13 @@
       <c r="J7" s="16"/>
     </row>
     <row r="8" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="45"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
       <c r="G8" s="2"/>
       <c r="H8" s="17" t="s">
         <v>14</v>
@@ -2241,11 +2241,11 @@
         <v>5</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="46" t="s">
+      <c r="H10" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="47"/>
-      <c r="J10" s="48"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="39"/>
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="2"/>
@@ -2312,12 +2312,12 @@
       </c>
     </row>
     <row r="15" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="45"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -2334,16 +2334,16 @@
       <c r="D16" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="46" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="34" t="s">
+      <c r="H16" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="35"/>
-      <c r="J16" s="36"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" s="22" t="s">
@@ -2355,7 +2355,7 @@
       <c r="D17" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="38"/>
+      <c r="E17" s="47"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="7" t="s">
@@ -2378,7 +2378,7 @@
       <c r="D18" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="38"/>
+      <c r="E18" s="47"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="24" t="s">
@@ -2401,7 +2401,7 @@
       <c r="D19" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="39"/>
+      <c r="E19" s="48"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="14" t="s">
@@ -2422,7 +2422,7 @@
       <c r="D20" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="40" t="s">
         <v>36</v>
       </c>
       <c r="F20" s="2"/>
@@ -2447,7 +2447,7 @@
       <c r="D21" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="32"/>
+      <c r="E21" s="41"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -2464,14 +2464,14 @@
       <c r="D22" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="32"/>
+      <c r="E22" s="41"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="I22" s="35"/>
-      <c r="J22" s="36"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="45"/>
     </row>
     <row r="23" spans="2:10" ht="17.25" thickBot="1">
       <c r="B23" s="26" t="s">
@@ -2483,7 +2483,7 @@
       <c r="D23" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="33"/>
+      <c r="E23" s="42"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="7" t="s">
@@ -2541,36 +2541,36 @@
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="2:10" ht="17" customHeight="1" thickBot="1">
-      <c r="B28" s="40" t="s">
+      <c r="B28" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="42"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="36"/>
     </row>
     <row r="29" spans="2:10" ht="17.25" thickBot="1">
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="45"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="46" t="s">
+      <c r="H30" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="I30" s="47"/>
-      <c r="J30" s="48"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="39"/>
     </row>
     <row r="31" spans="2:10">
       <c r="B31" s="3" t="s">
@@ -2636,13 +2636,13 @@
       <c r="J33" s="16"/>
     </row>
     <row r="34" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B34" s="43" t="s">
+      <c r="B34" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="45"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="33"/>
       <c r="G34" s="2"/>
       <c r="H34" s="17" t="s">
         <v>14</v>
@@ -2693,11 +2693,11 @@
         <v>5</v>
       </c>
       <c r="G36" s="2"/>
-      <c r="H36" s="46" t="s">
+      <c r="H36" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="47"/>
-      <c r="J36" s="48"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="39"/>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="2"/>
@@ -2764,12 +2764,12 @@
       </c>
     </row>
     <row r="41" spans="2:10" ht="17.25" thickBot="1">
-      <c r="B41" s="43" t="s">
+      <c r="B41" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="45"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="33"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -2786,16 +2786,16 @@
       <c r="D42" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="37" t="s">
+      <c r="E42" s="46" t="s">
         <v>25</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="34" t="s">
+      <c r="H42" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="I42" s="35"/>
-      <c r="J42" s="36"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="45"/>
     </row>
     <row r="43" spans="2:10">
       <c r="B43" s="22" t="s">
@@ -2807,7 +2807,7 @@
       <c r="D43" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="38"/>
+      <c r="E43" s="47"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="7" t="s">
@@ -2830,7 +2830,7 @@
       <c r="D44" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E44" s="38"/>
+      <c r="E44" s="47"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="24" t="s">
@@ -2853,7 +2853,7 @@
       <c r="D45" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="39"/>
+      <c r="E45" s="48"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="14" t="s">
@@ -2874,7 +2874,7 @@
       <c r="D46" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E46" s="31" t="s">
+      <c r="E46" s="40" t="s">
         <v>36</v>
       </c>
       <c r="F46" s="2"/>
@@ -2899,7 +2899,7 @@
       <c r="D47" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="32"/>
+      <c r="E47" s="41"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -2916,14 +2916,14 @@
       <c r="D48" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="32"/>
+      <c r="E48" s="41"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
-      <c r="H48" s="34" t="s">
+      <c r="H48" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="I48" s="35"/>
-      <c r="J48" s="36"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="45"/>
     </row>
     <row r="49" spans="2:10" ht="17.25" thickBot="1">
       <c r="B49" s="26" t="s">
@@ -2935,7 +2935,7 @@
       <c r="D49" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E49" s="33"/>
+      <c r="E49" s="42"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="7" t="s">
@@ -2987,12 +2987,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="H10:J10"/>
     <mergeCell ref="E46:E49"/>
     <mergeCell ref="H48:J48"/>
     <mergeCell ref="E16:E19"/>
@@ -3007,6 +3001,12 @@
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="E42:E45"/>
     <mergeCell ref="H42:J42"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="H10:J10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
